--- a/Catch and index models/desembarques_macarellus_1989_2025.xlsx
+++ b/Catch and index models/desembarques_macarellus_1989_2025.xlsx
@@ -14,11 +14,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="18">
   <si>
     <t>Yr</t>
   </si>
   <si>
+    <t>Desemb_total_t</t>
+  </si>
+  <si>
+    <t>fonte_total</t>
+  </si>
+  <si>
     <t>Catch_macarellus_t</t>
   </si>
   <si>
@@ -37,19 +43,31 @@
     <t>periodo</t>
   </si>
   <si>
+    <t>IMar total (todas as artes)</t>
+  </si>
+  <si>
     <t>Historico 1989-2014 (agregado)</t>
   </si>
   <si>
     <t>pre-alvo (&lt;=2014)</t>
   </si>
   <si>
+    <t>interpolado (total &lt; cerco)</t>
+  </si>
+  <si>
     <t>IMar viagem</t>
   </si>
   <si>
     <t>pos-alvo (&gt;=2015)</t>
   </si>
   <si>
+    <t>2018: media dos vizinhos</t>
+  </si>
+  <si>
     <t>IMar 2018 (formato diferente)</t>
+  </si>
+  <si>
+    <t>cerco (sem total no ano)</t>
   </si>
 </sst>
 </file>
@@ -392,10 +410,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:9" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -417,778 +435,1006 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>1989</v>
       </c>
       <c r="B2">
+        <v>1671</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2">
         <v>165.696</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>1990</v>
       </c>
       <c r="B3">
+        <v>1001</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
         <v>207.517</v>
       </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>1991</v>
       </c>
       <c r="B4">
+        <v>1263</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4">
         <v>242.225</v>
       </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>1992</v>
       </c>
       <c r="B5">
+        <v>2169</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
         <v>1116.246</v>
       </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>1993</v>
       </c>
       <c r="B6">
+        <v>1427</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6">
         <v>148.56</v>
       </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>1994</v>
       </c>
       <c r="B7">
+        <v>1948</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7">
         <v>671.263</v>
       </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>1995</v>
       </c>
       <c r="B8">
+        <v>1585</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8">
         <v>868.654</v>
       </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>1996</v>
       </c>
       <c r="B9">
+        <v>1751</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9">
         <v>966.037</v>
       </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>1997</v>
       </c>
       <c r="B10">
+        <v>2984</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10">
         <v>2194.416</v>
       </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>1998</v>
       </c>
       <c r="B11">
+        <v>3015</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
         <v>1882.119</v>
       </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>1999</v>
       </c>
       <c r="B12">
+        <v>2707</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12">
         <v>1622.012</v>
       </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>2000</v>
       </c>
       <c r="B13">
+        <v>1864</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13">
         <v>1075.395</v>
       </c>
-      <c r="D13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>2001</v>
       </c>
       <c r="B14">
+        <v>1379</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14">
         <v>847.7</v>
       </c>
-      <c r="D14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>2002</v>
       </c>
       <c r="B15">
+        <v>2232</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15">
         <v>1751.447</v>
       </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>2003</v>
       </c>
       <c r="B16">
+        <v>1830</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16">
         <v>1398.02</v>
       </c>
-      <c r="D16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>2004</v>
       </c>
       <c r="B17">
+        <v>1741</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17">
         <v>1085.991</v>
       </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>2005</v>
       </c>
       <c r="B18">
+        <v>2181</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18">
         <v>1460.566</v>
       </c>
-      <c r="D18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>2006</v>
       </c>
       <c r="B19">
+        <v>2627</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19">
         <v>1937.453</v>
       </c>
-      <c r="D19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>2007</v>
       </c>
       <c r="B20">
+        <v>2855</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20">
         <v>2292.716</v>
       </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>2008</v>
       </c>
       <c r="B21">
+        <v>2387</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21">
         <v>2033.549</v>
       </c>
-      <c r="D21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>2009</v>
       </c>
       <c r="B22">
+        <v>1771</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22">
         <v>1373.338</v>
       </c>
-      <c r="D22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>2010</v>
       </c>
       <c r="B23">
+        <v>1749</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23">
         <v>1442.3</v>
       </c>
-      <c r="D23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>2011</v>
       </c>
       <c r="B24">
+        <v>2163</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24">
         <v>1911.578</v>
       </c>
-      <c r="D24" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>2012</v>
       </c>
       <c r="B25">
+        <v>2643</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25">
         <v>2488.848</v>
       </c>
-      <c r="D25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>2013</v>
       </c>
       <c r="B26">
+        <v>2214</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26">
         <v>2210.106</v>
       </c>
-      <c r="D26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="F26" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>2014</v>
       </c>
       <c r="B27">
+        <v>1429</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27">
         <v>1273.775</v>
       </c>
-      <c r="D27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28">
         <v>2015</v>
       </c>
       <c r="B28">
+        <v>644</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28">
         <v>24.05</v>
       </c>
-      <c r="C28">
+      <c r="E28">
         <v>172.812</v>
       </c>
-      <c r="D28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29">
         <v>2016</v>
       </c>
       <c r="B29">
+        <v>650</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29">
         <v>186.57</v>
       </c>
-      <c r="C29">
+      <c r="E29">
         <v>852.405</v>
       </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30">
         <v>2017</v>
       </c>
       <c r="B30">
+        <v>657</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30">
         <v>621.994</v>
       </c>
-      <c r="C30">
+      <c r="E30">
         <v>5088.002</v>
       </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31">
         <v>2018</v>
       </c>
       <c r="B31">
+        <v>554.5</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31">
         <v>2216.99</v>
       </c>
-      <c r="C31">
+      <c r="E31">
         <v>7968.823</v>
       </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="G31" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="F31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32">
         <v>2019</v>
       </c>
       <c r="B32">
+        <v>806</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32">
         <v>793.841</v>
       </c>
-      <c r="C32">
+      <c r="E32">
         <v>4335.592</v>
       </c>
-      <c r="D32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33">
         <v>2020</v>
       </c>
       <c r="B33">
+        <v>410</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33">
         <v>411.605</v>
       </c>
-      <c r="C33">
+      <c r="E33">
         <v>4652.124</v>
       </c>
-      <c r="D33" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34">
         <v>2021</v>
       </c>
       <c r="B34">
+        <v>160</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34">
         <v>155.539</v>
       </c>
-      <c r="C34">
+      <c r="E34">
         <v>6395.932</v>
       </c>
-      <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35">
         <v>2022</v>
       </c>
       <c r="B35">
+        <v>176</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35">
         <v>151.855</v>
       </c>
-      <c r="C35">
+      <c r="E35">
         <v>4396.978</v>
       </c>
-      <c r="D35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36">
         <v>2023</v>
       </c>
       <c r="B36">
+        <v>248</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36">
         <v>214.405</v>
       </c>
-      <c r="C36">
+      <c r="E36">
         <v>4107.807</v>
       </c>
-      <c r="D36" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="F36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37">
         <v>2024</v>
       </c>
       <c r="B37">
         <v>286.399</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37">
+        <v>286.399</v>
+      </c>
+      <c r="E37">
         <v>3987.596</v>
       </c>
-      <c r="D37" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" t="b">
-        <v>1</v>
-      </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38">
         <v>2025</v>
       </c>
       <c r="B38">
         <v>61.892</v>
       </c>
-      <c r="C38">
+      <c r="C38" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38">
+        <v>61.892</v>
+      </c>
+      <c r="E38">
         <v>3211.91</v>
       </c>
-      <c r="D38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" t="s">
-        <v>10</v>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
